--- a/ejemplo/Ejemplo_EST.xlsx
+++ b/ejemplo/Ejemplo_EST.xlsx
@@ -43,30 +43,55 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tamaño MEP</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Longitud (m)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área (m²)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área bruta (m²)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Volumen (m³)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Material estructural</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Volumen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t xml:space="preserve">Área</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo: b</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo: Coste</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo: h</t>
         </is>
@@ -103,17 +128,23 @@
           <t xml:space="preserve">Planta baja</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2">
+        <v>240.0</v>
+      </c>
+      <c r="K2">
+        <v>84.0</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">84,00 m³</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t xml:space="preserve">240,00 m²</t>
         </is>
@@ -150,27 +181,30 @@
           <t xml:space="preserve">Planta baja</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,00</t>
-        </is>
+      <c r="K3">
+        <v>0.26</v>
       </c>
       <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -207,27 +241,30 @@
           <t xml:space="preserve">Planta baja</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,00</t>
-        </is>
+      <c r="K4">
+        <v>0.26</v>
       </c>
       <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -264,27 +301,30 @@
           <t xml:space="preserve">Planta baja</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,00</t>
-        </is>
+      <c r="K5">
+        <v>0.26</v>
       </c>
       <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -321,27 +361,30 @@
           <t xml:space="preserve">Planta baja</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,00</t>
-        </is>
+      <c r="K6">
+        <v>0.26</v>
       </c>
       <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -378,27 +421,30 @@
           <t xml:space="preserve">Planta baja</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,00</t>
-        </is>
+      <c r="K7">
+        <v>0.26</v>
       </c>
       <c r="L7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -435,27 +481,30 @@
           <t xml:space="preserve">Planta baja</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,00</t>
-        </is>
+      <c r="K8">
+        <v>0.26</v>
       </c>
       <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -492,17 +541,23 @@
           <t xml:space="preserve">Planta 1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9">
+        <v>240.0</v>
+      </c>
+      <c r="K9">
+        <v>84.0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">84,00 m³</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t xml:space="preserve">240,00 m²</t>
         </is>
@@ -539,27 +594,30 @@
           <t xml:space="preserve">Planta 1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,00</t>
-        </is>
+      <c r="K10">
+        <v>0.26</v>
       </c>
       <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -596,27 +654,30 @@
           <t xml:space="preserve">Planta 1</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,00</t>
-        </is>
+      <c r="K11">
+        <v>0.26</v>
       </c>
       <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -653,27 +714,30 @@
           <t xml:space="preserve">Planta 1</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,00</t>
-        </is>
+      <c r="K12">
+        <v>0.26</v>
       </c>
       <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -710,27 +774,30 @@
           <t xml:space="preserve">Planta 1</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,00</t>
-        </is>
+      <c r="K13">
+        <v>0.26</v>
       </c>
       <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -767,27 +834,30 @@
           <t xml:space="preserve">Planta 1</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,00</t>
-        </is>
+      <c r="K14">
+        <v>0.26</v>
       </c>
       <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -824,27 +894,30 @@
           <t xml:space="preserve">Planta 1</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,00</t>
-        </is>
+      <c r="K15">
+        <v>0.26</v>
       </c>
       <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -881,17 +954,23 @@
           <t xml:space="preserve">Planta 2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16">
+        <v>240.0</v>
+      </c>
+      <c r="K16">
+        <v>84.0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">84,00 m³</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t xml:space="preserve">240,00 m²</t>
         </is>
@@ -928,27 +1007,30 @@
           <t xml:space="preserve">Planta 2</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,00</t>
-        </is>
+      <c r="K17">
+        <v>0.26</v>
       </c>
       <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -985,27 +1067,30 @@
           <t xml:space="preserve">Planta 2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,00</t>
-        </is>
+      <c r="K18">
+        <v>0.26</v>
       </c>
       <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -1042,27 +1127,30 @@
           <t xml:space="preserve">Planta 2</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,00</t>
-        </is>
+      <c r="K19">
+        <v>0.26</v>
       </c>
       <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -1099,27 +1187,30 @@
           <t xml:space="preserve">Planta 2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,00</t>
-        </is>
+      <c r="K20">
+        <v>0.26</v>
       </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -1156,27 +1247,30 @@
           <t xml:space="preserve">Planta 2</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,00</t>
-        </is>
+      <c r="K21">
+        <v>0.26</v>
       </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -1213,27 +1307,30 @@
           <t xml:space="preserve">Planta 2</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,00</t>
-        </is>
+      <c r="K22">
+        <v>0.26</v>
       </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>

--- a/ejemplo/Ejemplo_EST.xlsx
+++ b/ejemplo/Ejemplo_EST.xlsx
@@ -68,32 +68,57 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t xml:space="preserve">W (kg/m)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Peso (kg)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Longitud</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Longitud de corte</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Material estructural</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t xml:space="preserve">Volumen</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t xml:space="preserve">Área</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo: b</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo: Coste</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo: h</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tipo: W</t>
         </is>
       </c>
     </row>
@@ -134,17 +159,17 @@
       <c r="K2">
         <v>84.0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t xml:space="preserve">84,00 m³</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t xml:space="preserve">240,00 m²</t>
         </is>
@@ -184,27 +209,27 @@
       <c r="K3">
         <v>0.26</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0,00</t>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -244,27 +269,27 @@
       <c r="K4">
         <v>0.26</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0,00</t>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -304,27 +329,27 @@
       <c r="K5">
         <v>0.26</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve">0,00</t>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -364,27 +389,27 @@
       <c r="K6">
         <v>0.26</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve">0,00</t>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -424,27 +449,27 @@
       <c r="K7">
         <v>0.26</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve">0,00</t>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -484,27 +509,27 @@
       <c r="K8">
         <v>0.26</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0,00</t>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -547,17 +572,17 @@
       <c r="K9">
         <v>84.0</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t xml:space="preserve">84,00 m³</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t xml:space="preserve">240,00 m²</t>
         </is>
@@ -597,27 +622,27 @@
       <c r="K10">
         <v>0.26</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t xml:space="preserve">0,00</t>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -657,27 +682,27 @@
       <c r="K11">
         <v>0.26</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0,00</t>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -717,27 +742,27 @@
       <c r="K12">
         <v>0.26</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t xml:space="preserve">0,00</t>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -777,27 +802,27 @@
       <c r="K13">
         <v>0.26</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t xml:space="preserve">0,00</t>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -837,27 +862,27 @@
       <c r="K14">
         <v>0.26</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t xml:space="preserve">0,00</t>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -897,27 +922,27 @@
       <c r="K15">
         <v>0.26</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t xml:space="preserve">0,00</t>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -960,17 +985,17 @@
       <c r="K16">
         <v>84.0</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="P16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t xml:space="preserve">84,00 m³</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t xml:space="preserve">240,00 m²</t>
         </is>
@@ -1010,27 +1035,27 @@
       <c r="K17">
         <v>0.26</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t xml:space="preserve">0,00</t>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -1070,27 +1095,27 @@
       <c r="K18">
         <v>0.26</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t xml:space="preserve">0,00</t>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -1130,27 +1155,27 @@
       <c r="K19">
         <v>0.26</v>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0,00</t>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -1190,27 +1215,27 @@
       <c r="K20">
         <v>0.26</v>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t xml:space="preserve">0,00</t>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -1250,27 +1275,27 @@
       <c r="K21">
         <v>0.26</v>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t xml:space="preserve">0,00</t>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
@@ -1310,29 +1335,299 @@
       <c r="K22">
         <v>0.26</v>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HA-25/B/20/IIa</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0,26 m³</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t xml:space="preserve">0,00</t>
+          <t xml:space="preserve">HA-25/B/20/IIa</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t xml:space="preserve">300 mm</t>
+          <t xml:space="preserve">0,26 m³</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0,00</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">310280</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5e2a0004bc08-0000</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armazón estructural</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viga-IPE</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IPE300</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planta 2</t>
+        </is>
+      </c>
+      <c r="H23">
+        <v>20.0</v>
+      </c>
+      <c r="L23">
+        <v>42.2</v>
+      </c>
+      <c r="M23">
+        <v>831.34</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20,00 m</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19,70 m</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42,20 kg/m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">310287</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5e2a0004bc0f-0000</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armazón estructural</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viga-IPE</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IPE300</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planta 2</t>
+        </is>
+      </c>
+      <c r="H24">
+        <v>20.0</v>
+      </c>
+      <c r="L24">
+        <v>42.2</v>
+      </c>
+      <c r="M24">
+        <v>831.34</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20,00 m</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19,70 m</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42,20 kg/m</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">310294</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5e2a0004bc16-0000</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armazón estructural</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viga-IPE</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IPE300</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planta 2</t>
+        </is>
+      </c>
+      <c r="H25">
+        <v>20.0</v>
+      </c>
+      <c r="L25">
+        <v>42.2</v>
+      </c>
+      <c r="M25">
+        <v>831.34</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20,00 m</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19,70 m</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42,20 kg/m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">310301</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5e2a0004bc1d-0000</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pilares estructurales</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pilar-HEB</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEB200</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planta baja</t>
+        </is>
+      </c>
+      <c r="H26">
+        <v>3.2</v>
+      </c>
+      <c r="L26">
+        <v>61.3</v>
+      </c>
+      <c r="M26">
+        <v>196.16</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3,20 m</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61,30 kg/m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">310308</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5e2a0004bc24-0000</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pilares estructurales</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pilar-HEB</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEB200</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planta baja</t>
+        </is>
+      </c>
+      <c r="H27">
+        <v>3.2</v>
+      </c>
+      <c r="L27">
+        <v>61.3</v>
+      </c>
+      <c r="M27">
+        <v>196.16</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3,20 m</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61,30 kg/m</t>
         </is>
       </c>
     </row>
